--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CAPA BANCO- 26_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CAPA BANCO- 26_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -453,7 +448,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +464,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -487,7 +480,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -504,7 +496,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -521,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -538,7 +528,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -555,7 +544,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -572,7 +560,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -589,7 +576,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -598,7 +584,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CAPA BANCO RRMOTOS CAPA BANCOX250 TWISTER</t>
+          <t>CAPA BANCO RRMOTOS CBX250 TWISTER</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -606,7 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -619,7 +604,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CAPA BANCO STILUS PCX 2016 EM DIANTE</t>
+          <t>CAPA BANCO STYLUS PCX 2016 EM DIANTE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -627,7 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -648,7 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -661,7 +644,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CAPA BANCO STILUS BROS NXR 2009 A 2014</t>
+          <t>CAPA BANCO STYLUS BROS NXR 2009 A 2014</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -669,7 +652,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -690,11 +672,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -707,7 +684,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CAPA BANCO RRMOTOS CAPA BANCOX250 TWISTER</t>
+          <t>CAPA BANCO RRMOTOS CAPA BANCO CBX250 TWISTER</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -715,7 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -736,7 +712,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -757,7 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -774,7 +748,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -795,7 +768,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -816,7 +788,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -837,7 +808,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -858,11 +828,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -883,7 +848,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -900,7 +864,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -921,7 +884,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -933,21 +895,31 @@
           <t xml:space="preserve">CAPA BANCO BAHIA </t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7899738015256</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>CAPA BANCO PIRACAPAS AZUL PCX150 2016 A 2021</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
